--- a/data/template0523/报价系统功能基础数据功能结构所需字段（3.0版）.xlsx
+++ b/data/template0523/报价系统功能基础数据功能结构所需字段（3.0版）.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-joii\project\CPQ-superpowers\dev\data\报价相关\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-joii\project\CPQ-superpowers-v2\dev\docs\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3565940-AA6C-49F5-88CA-F15F30711633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="912" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素单价" sheetId="1" r:id="rId1"/>
@@ -32,7 +33,7 @@
     <sheet name="单重" sheetId="9" r:id="rId18"/>
     <sheet name="年降系数" sheetId="16" r:id="rId19"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="198">
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -290,38 +291,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>施耐德</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计算报价时间的上一个月平均</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.baiinfo.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>百川盈孚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算报价的前一天的峰值平均</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>施耐德</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4NEG5304704</t>
   </si>
   <si>
@@ -329,14 +302,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>KG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>年降系数（%/年）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -410,10 +375,6 @@
   </si>
   <si>
     <t>拒收率/不良率（%）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（先不填）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -810,70 +771,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>元素BOM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来料固定加工费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来料其他费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>来料年降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成品固定加工费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成品其他费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组成件BOM及单价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组装加工费年降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电镀方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电镀费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单重</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年降系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素回收折扣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回收折扣（%）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>来料回收折扣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>回收折扣（%）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -886,10 +787,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>组成件其他费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>要素编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -954,14 +851,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>?</t>
+    <t>基准值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>New Tools-12 Ref Approved</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4NEG5304705</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
@@ -1030,10 +935,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -1070,7 +973,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1090,6 +993,21 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1134,12 +1052,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1421,23 +1339,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.375" customWidth="1"/>
+    <col min="2" max="2" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1460,16 +1378,16 @@
         <v>4</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>8000137</v>
       </c>
@@ -1495,254 +1413,313 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>8000143</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="4">
-        <v>400</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>8000143</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="4">
-        <v>100</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9991</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="C3" s="4">
+        <v>9992</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>188</v>
+      </c>
       <c r="H3" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3120012588</v>
+        <v>3120012574</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4">
+        <v>9993</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>219</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="H4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>3120012588</v>
+        <v>3120012574</v>
       </c>
       <c r="B5" s="4">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9994</v>
+      </c>
       <c r="D5" s="4" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>194</v>
+      </c>
       <c r="G5" s="4" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H5" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <v>3120012588</v>
+        <v>3120012575</v>
       </c>
       <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>216</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
+        <v>9951</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="4">
         <v>5</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
+        <v>9951</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="4">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4">
+        <v>9953</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>9954</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="4">
+        <v>5</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1754,117 +1731,184 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="B1" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
       <c r="B3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3120012574</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>3120012574</v>
       </c>
       <c r="B5" s="4">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>3120012574</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B9" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="4">
         <v>0.4</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>141</v>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1874,185 +1918,335 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>8881</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="F3" s="4">
+        <v>8882</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="H3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E4" s="4">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="F4" s="4">
+        <v>8883</v>
+      </c>
       <c r="G4" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>8884</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>8885</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8851</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8852</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="4">
+        <v>2</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="4">
         <v>3</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="F9" s="4">
+        <v>8853</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" s="4">
         <v>3</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="4">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="4">
-        <v>2</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>75</v>
+      <c r="I9" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>8854</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>8855</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2062,231 +2256,277 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:O15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" customWidth="1"/>
-    <col min="12" max="12" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" customWidth="1"/>
-    <col min="14" max="14" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.625" customWidth="1"/>
+    <col min="14" max="14" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>8881</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="O2" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4">
+        <v>8881</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="M3" s="4">
-        <v>7.0000000000000001E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4">
+        <v>8881</v>
+      </c>
       <c r="G4" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="M4" s="4">
-        <v>2E-3</v>
+        <v>0.2</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>8882</v>
+      </c>
       <c r="G5" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <v>8883</v>
+      </c>
       <c r="G6" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -2294,146 +2534,426 @@
         <v>1</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="M6" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8884</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8885</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4">
+        <v>8851</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="M9" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>8851</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M10" s="4">
+        <v>2E-3</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>8851</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="4">
+        <v>3</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>8852</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M12" s="4">
         <v>0.05</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="N12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="M7" s="4">
+      <c r="F13" s="4">
+        <v>8853</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M13" s="4">
         <v>1E-3</v>
       </c>
-      <c r="N7" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="4">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="M8" s="4">
+      <c r="N13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>8854</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="4">
         <v>1.2</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" s="4">
-        <v>2</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="N14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>8855</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M15" s="4">
         <v>0.3</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>75</v>
+      <c r="N15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2443,90 +2963,129 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F2" s="2" t="s">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="4">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="D3" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" s="4">
+        <v>45</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="4">
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="4">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2536,132 +3095,208 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>1.4999999999999999E-2</v>
+        <v>2E-3</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3100090137</v>
+        <v>3120012574</v>
       </c>
       <c r="B4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4">
         <v>2E-3</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>3100090137</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4">
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I7" s="4">
         <v>2</v>
       </c>
     </row>
@@ -2672,196 +3307,212 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2000</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3.1E-2</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4">
         <v>2000</v>
       </c>
       <c r="C3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H3" s="4">
-        <v>3.1E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2000</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="4">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="J4" s="4" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
-    <hyperlink ref="E4" r:id="rId2"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0F00-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.125" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D2" s="4">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4">
+        <v>120</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090136</v>
+        <v>3120012575</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4">
         <v>2000</v>
       </c>
       <c r="D3" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="4">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>10</v>
@@ -2877,33 +3528,36 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090136</v>
+        <v>3120012575</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -2913,81 +3567,76 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3100090136</v>
+        <v>3120012574</v>
       </c>
       <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G3" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3100080145</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="4">
         <v>2</v>
       </c>
     </row>
@@ -2998,50 +3647,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4">
         <v>102000966</v>
@@ -3050,15 +3699,41 @@
         <v>3120012574</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H2" s="4">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="4">
+        <v>102000967</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="4">
         <v>7.12</v>
       </c>
     </row>
@@ -3069,67 +3744,69 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>3120012574</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
+      <c r="C2" s="4">
+        <v>9997</v>
+      </c>
       <c r="D2" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>11</v>
@@ -3138,7 +3815,7 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I2" s="4">
         <v>5</v>
@@ -3147,16 +3824,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4">
+        <v>9998</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>48</v>
@@ -3168,12 +3847,76 @@
         <v>50</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="I3" s="4">
         <v>5</v>
       </c>
       <c r="J3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>9957</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4">
+        <v>5</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9958</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4">
+        <v>120</v>
+      </c>
+      <c r="G5" s="4">
+        <v>50</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4">
+        <v>5</v>
+      </c>
+      <c r="J5" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3185,173 +3928,284 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>9996</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="F2" s="4">
+        <v>75</v>
+      </c>
+      <c r="G2" s="4">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4">
+        <v>9996</v>
+      </c>
       <c r="C3" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F3" s="4">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G3" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3120012574</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="4">
+        <v>9995</v>
+      </c>
       <c r="C4" s="4" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F4" s="4">
-        <v>25</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>3120012574</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4">
+        <v>9995</v>
+      </c>
       <c r="C5" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F5" s="4">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="4">
-        <v>1.25</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0.98</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <v>3120012574</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>3120012575</v>
+      </c>
+      <c r="B6" s="4">
+        <v>9956</v>
+      </c>
       <c r="C6" s="4" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="D6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="F6" s="4">
-        <v>30</v>
-      </c>
-      <c r="G6" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F16" t="s">
-        <v>221</v>
-      </c>
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>9956</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="4">
+        <v>25</v>
+      </c>
+      <c r="G7" s="4">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B8" s="4">
+        <v>9955</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="4">
+        <v>70</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B9" s="4">
+        <v>9955</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="4">
+        <v>30</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3361,76 +4215,115 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="C1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>9996</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="4">
+        <v>9996</v>
+      </c>
       <c r="C3" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="F3" s="4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
-        <v>3120012574</v>
-      </c>
-      <c r="B4" s="4"/>
+        <v>3120012575</v>
+      </c>
+      <c r="B4" s="4">
+        <v>9956</v>
+      </c>
       <c r="C4" s="4" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B5" s="4">
+        <v>9956</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="4">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3440,139 +4333,204 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9997</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+      <c r="E2" s="4">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J2" s="4">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
       <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>84</v>
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>9998</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E3" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="J3" s="4">
+        <v>58</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4">
+        <v>10</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>9957</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4">
         <v>5</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3120012574</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4">
+        <v>162</v>
+      </c>
+      <c r="J4" s="4">
+        <v>5</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9958</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>171</v>
+      <c r="I5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4">
+        <v>10</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3583,158 +4541,272 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="B1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I1" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9997</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
       <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>9998</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3120012574</v>
       </c>
       <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4">
+        <v>9998</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>3120012574</v>
       </c>
       <c r="B5" s="4">
         <v>2</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="4">
+        <v>9998</v>
+      </c>
       <c r="D5" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
-        <v>3120012574</v>
+        <v>3120012575</v>
       </c>
       <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
+        <v>9957</v>
+      </c>
       <c r="D6" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4">
         <v>3</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4">
+        <v>9958</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4">
+        <v>9958</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4">
+        <v>23</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>9958</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.4</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>178</v>
-      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3743,139 +4815,230 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="14" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="C1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9997</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>3120012574</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4">
+        <v>9997</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="4">
-        <v>1.4999999999999999E-2</v>
+        <v>2E-3</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3120012574</v>
       </c>
       <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>9998</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E4" s="4">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>9957</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
+        <v>9957</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
         <v>2E-3</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>3120012574</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>3120012575</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4">
+        <v>9958</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4">
         <v>3</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="H7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J7" s="4">
         <v>2</v>
       </c>
     </row>
@@ -3886,51 +5049,63 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="B1" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="D1" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>3120012574</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>9998</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
-        <v>3120012574</v>
+        <v>3120012575</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>84</v>
+      <c r="C3" s="4">
+        <v>9958</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E3" s="4">
         <v>10</v>
